--- a/extenbooks/S1402_extenbook.xlsx
+++ b/extenbooks/S1402_extenbook.xlsx
@@ -7258,7 +7258,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Status**: ingested · **Authored**: 2026-05-18</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -8185,11 +8185,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8212,76 +8212,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Unemployment Measures US 1948-2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1402_research.json", "adequacy_report": "Technical/docs/chapters/CH14_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1402_DPR.md", "epr": "Technical/docs/series/S1402_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1402_load.py", "processor": "Technical/code/P02_processors/P02_S1402_construct.py", "validator": "Technical/code/V03_validators/V03_S1402_validate.py", "processed": "Technical/data/processed/S1402.parquet", "chopped_csv": "Technical/chopped/S1402.csv", "extenbook_xlsx": "Technical/extenbooks/S1402_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:58:43.529185+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1402_extenbook.xlsx
+++ b/extenbooks/S1402_extenbook.xlsx
@@ -656,7 +656,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>index_1948_1951_avg=100</t>
+          <t>index_1948_1951_avg=1</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A94"/>
+  <dimension ref="A1:A101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7234,7 +7234,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t># S1402 — Unemployment Measures, US 1948-2011</t>
+          <t># S1402 — Unemployment Measures, United States</t>
         </is>
       </c>
     </row>
@@ -7244,14 +7244,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Data Provenance Record (DPR)**</t>
+          <t>**Data Provenance Record**</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion) · **Chapter**: 14 · **Figure**: 14.11</t>
+          <t>**Pipeline stage**: Ingestion · **Chapter**: 14 · **Figure**: 14.11</t>
         </is>
       </c>
     </row>
@@ -7263,299 +7263,295 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>## 1. Definition</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S1402 jointly publishes the three unemployment measures plotted in Fig 14.11:</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>- **S1402-A** Civilian unemployment rate (decimal, BLS CPS LNS14000000)</t>
+          <t>S1402 jointly publishes the three unemployment measures plotted in Fig 14.11:</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- **S1402-B** Duration index (BLS CPS LNS13008275, mean weeks, rebased 1948-1951=100)</t>
+          <t>- **S1402-A** Civilian unemployment rate (decimal, BLS CPS LNS14000000)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- **S1402-C** Unemployment intensity = rate * (duration_index/100) -- Shaikh's Eq. 14.13</t>
+          <t>- **S1402-B** Duration index (BLS CPS LNS13008275, mean weeks, rebased so 1948-1951 average = 1)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>- **S1402-C** Unemployment intensity = rate * duration_index -- Shaikh's Eq. 14.13</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>## 2. Why it matters</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unemployment intensity (Shaikh's invention) is the x-axis of every Phillips</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>curve in Section V (S1404-S1408). Shaikh argues it captures wage-suppression</t>
+          <t>Unemployment intensity (Shaikh's invention) is the x-axis of every Phillips</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pressure better than the unemployment rate alone because long-spell</t>
+          <t>curve in Section V (S1404-S1408). Shaikh argues it captures wage-suppression</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>pressure better than the unemployment rate alone because long-spell</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>unemployment multiplies the effective slack.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>## 3. Sources</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| S1402-A | 1948-2011 | Appendix 14.3 `UNEMPLRATE` (BLS LNS14000000) | decimal | Salvaged xlsx |</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1402-A, S1402-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>| S1402-B | 1948-2011 | Appendix 14.3 `UNEMPDURATION` (BLS LNS13008275 rebased) | index 1948-51 avg=100 | Salvaged xlsx |</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>| S1402-C | 1948-2011 | Appendix 14.3 `ulintensity` (derived) | decimal | Salvaged xlsx |</t>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>| S1402-D | 1948-2024 | FRED `UNRATE` (monthly to annual mean) | percent | Live API |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>| S1402-E | 1948-2024 | FRED `UEMPMEAN` (monthly to annual mean) | weeks | Live API |</t>
+          <t>| S1402-A | 1948-2025 | Appendix 14.3 `UNEMPLRATE` (BLS LNS14000000); FRED `UNRATE` for extension | decimal rate | Salvaged xlsx + Live API |</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>| S1402-B | 1948-2025 | Appendix 14.3 `UNEMPDURATION` (BLS LNS13008275 rebased); FRED `UEMPMEAN` for extension | index 1948-51 avg=1 | Salvaged xlsx + Live API |</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| S1402-C | 1948-2025 | Appendix 14.3 `ulintensity` (derived) | decimal | Salvaged xlsx + Live API |</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Composite. Formulas (Appendix 14.2 p. 892 verbatim):</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>duration_index_t = (UEMPMEAN_t / mean(UEMPMEAN_{1948..1951})) * 100   # index</t>
+          <t>Composite. Formula (algebraically equivalent to Appendix 14.2 p. 892; the</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>intensity_t      = UNRATE_t(decimal) * (duration_index_t / 100)        # decimal</t>
+          <t>stored duration index uses base=1 rather than base=100, so the two /100 and</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>*100 scalings cancel and intensity = rate * duration_index directly):</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>```</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>duration_index_t = UEMPMEAN_t / mean(UEMPMEAN_{1948..1951})   # base-1 index</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Book: 1948-2011 (64 obs each). Extension: 2012-2024 via FRED re-derivation.</t>
+          <t>intensity_t      = UNRATE_t(decimal) * duration_index_t        # decimal</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Rate decimal, duration index 1948-1951=100, intensity decimal.</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Book: 1948-2011 (64 obs each). Extension: 2012-2025 via FRED re-derivation.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1. **UEMPMEAN 2011-01 top-coding break**: BLS raised individual-respondent top-</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coded duration from 104w to 260w in January 2011. Per Phase 4 Q2 resolution,</t>
+          <t>Rate decimal, duration index 1948-1951 average = 1, intensity decimal.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   NO backward adjustment is applied; the break is annotated in the registry</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">   under `S1402.components.duration.methodological_break_2011-01: true`. The</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   duration INDEX absorbs part of the level shift via its rebased base period.</t>
+          <t>1. **UEMPMEAN 2011-01 top-coding break**: BLS raised individual-respondent top-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2. **No backward adjustment**: any analyst-estimated continuity correction</t>
+          <t xml:space="preserve">   coded duration from 104w to 260w in January 2011. Per the data-adequacy review,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   would alter Shaikh's published pre-2011 numbers, defeating the replication.</t>
+          <t xml:space="preserve">   NO backward adjustment is applied; the break is annotated in the registry</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   under `S1402.components.duration.methodological_break_2011-01: true`. The</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t xml:space="preserve">   duration INDEX absorbs part of the level shift via its rebased base period.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CD legacy `S069`, CD2 `S069`. Book pp. 663-664, 892. Figure 14.11.</t>
+          <t>2. **No backward adjustment**: any analyst-estimated continuity correction</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sibling: S1401 (wage share, the y-axis of Section V Phillips curves).</t>
+          <t xml:space="preserve">   would alter Shaikh's published pre-2011 numbers, defeating the replication.</t>
         </is>
       </c>
     </row>
@@ -7565,92 +7561,92 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>Predecessor builds: `S069`. Book pp. 663-664, 892. Figure 14.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sibling: S1401 (wage share, the y-axis of Section V Phillips curves).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Per-subseries units (registry units field is per_subseries, NOT a mixed_*</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>string): A=rate(decimal), B=index(1948-1951 avg=1), C=intensity(decimal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Tolerance ±1.0%; pass-through against Appendix 14.3.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4">
+    <row r="67">
+      <c r="A67" s="4">
         <f>== EPR: S1402_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t># S1402 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>**Series**: S1402 (Unemployment Measures) · **Chapter**: 14 · **Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>## Classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>`content_type: time_series` · `construction: composite` · extension applies.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-    </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Re-derivation. For 2012+, fetch FRED `UNRATE` and `UEMPMEAN` (both monthly,</t>
+          <t>**Series**: S1402 (Unemployment Measures) · **Chapter**: 14 · **Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>aggregated to annual means); rebase the duration index to the 1948-1951 mean</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>of FRED `UEMPMEAN` (already available in the same fetch); construct intensity</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>via Shaikh's exact formula.</t>
+          <t>`content_type: time_series` · `construction: composite` · extension applies.</t>
         </is>
       </c>
     </row>
@@ -7660,62 +7656,66 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>## Worked example</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2024: UNRATE mean ≈ 4.0% → 0.0400; UEMPMEAN mean ≈ 22.0 weeks; 1948-1951</t>
+          <t>Re-derivation. For 2012+, fetch FRED `UNRATE` and `UEMPMEAN` (both monthly,</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>base mean ≈ 11.5 weeks; duration index ≈ 1.913; intensity ≈ 0.0765.</t>
+          <t>aggregated to annual means); rebase the duration index to the 1948-1951 mean</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>of FRED `UEMPMEAN` (already available in the same fetch); construct intensity</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>## No-Proxy disclosure</t>
+          <t>via Shaikh's exact formula.</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>None. Both FRED IDs are the BLS CPS series Shaikh cites.</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>## Worked example</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>## No-Synthetic disclosure</t>
+          <t>2024: UNRATE mean ≈ 4.0% → 0.0400; UEMPMEAN mean ≈ 22.0 weeks; 1948-1951</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Every value is a primary BLS observation (book period via Appendix 14.3,</t>
+          <t>base mean ≈ 11.5 weeks; duration index (base=1) ≈ 1.913; intensity =</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>extension via FRED). No interpolation, no synthetic continuity correction.</t>
+          <t>rate * duration_index ≈ 0.0400 * 1.913 ≈ 0.0765.</t>
         </is>
       </c>
     </row>
@@ -7725,42 +7725,38 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>## Failure-mode table</t>
+          <t>## No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| Mode | Trigger | Behaviour |</t>
+          <t>None. Both FRED IDs are the BLS CPS series Shaikh cites.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>| FRED key missing | env unset | Extension skipped; book period only |</t>
+          <t>## No-Synthetic disclosure</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>| UEMPMEAN 2011 break | data semantics | Documented; no adjustment per Q2 resolution |</t>
+          <t>Every value is a primary BLS observation (book period via Appendix 14.3,</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>| Base window pre-1948 unavailable | not a real risk | Base is fixed at 1948-1951 from the data itself |</t>
+          <t>extension via FRED). No interpolation, no synthetic continuity correction.</t>
         </is>
       </c>
     </row>
@@ -7770,14 +7766,59 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>## CD2 divergence pre-disclosure</t>
+          <t>## Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Minimal expected (&lt;1%). CD2 used the same FRED series.</t>
+          <t>| Mode | Trigger | Behaviour |</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>| FRED key missing | env unset | Extension skipped; book period only |</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>| UEMPMEAN 2011 break | data semantics | Documented; no adjustment per the data-adequacy review |</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>| Base window pre-1948 unavailable | not a real risk | Base is fixed at 1948-1951 from the data itself |</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>## Divergence from the predecessor build</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Minimal expected (&lt;1%). The predecessor build used the same FRED series.</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8211,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T23:18:41.331189+00:00</t>
+          <t>2026-07-10T14:18:44.864290+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1402_extenbook.xlsx
+++ b/extenbooks/S1402_extenbook.xlsx
@@ -7258,7 +7258,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-10T14:18:44.864290+00:00</t>
+          <t>2026-07-11T03:44:22.884987+00:00</t>
         </is>
       </c>
     </row>
@@ -8226,11 +8226,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8253,6 +8253,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_14_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>validated_book_and_extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.14 Figure 14.11 (Unemployment Measures, United States, 1948-2011). Real data present in chopped CSV (234 points, 3 subseries A/B/C x 78 years, 1948-2025); book_period_validated; figure number and quotes KB-verified (Fig 14.11 quote verbatim at ch14 KB line 1417/1348; intensity definition Eq.14.13 at KB line 1273; sources at Appendix 14.2). MIXED_UNITS flag CONFIRMED and resolved: the three subseries carry three genuinely different units (rate=decimal, duration=index, intensity=decimal), so the banned registry units string 'mixed_unemployment_measures' is replaced by per-subseries units (field_fixes.units=per_subseries). UNITS CORRECTION: subseries S1402-B was labelled units='index_1948_1951_avg=100' but the chopped data is on base=1.0 (verified: 1948-1951 mean = 0.9998, and intensity C = A x B with B on base-1, NOT A x B/100). The 'avg=100' label was wrong by a factor of 100; corrected to base-1 index. NOTE the DPR S6 and research-JSON formula state the index as *100 (base=100) while the data is stored base-1 -- a doc/data reconciliation item flagged below; the published per-subseries unit matches the actual data.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1402_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1402_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UEMPMEAN 2011-01 top-coding break documented; no backward adjustment per Phase 4 Q2 resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
